--- a/site/User-Actions-on-Integrations/headings.xlsx
+++ b/site/User-Actions-on-Integrations/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -705,7 +705,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Show Code</t>
+          <t>References</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,32 +715,10 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01JACYG978Y8AMV9GEAQNWBJF6</t>
+          <t>h_01H02H9WB603XRNADRN1EK60SB</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Actions-on-Integrations/#h_01JACYG978Y8AMV9GEAQNWBJF6</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>References</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>h_01H02H9WB603XRNADRN1EK60SB</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Actions-on-Integrations/#h_01H02H9WB603XRNADRN1EK60SB</t>
         </is>

--- a/site/User-Actions-on-Integrations/headings.xlsx
+++ b/site/User-Actions-on-Integrations/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,7 +551,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>View Logs</t>
+          <t>Edit Integration Details</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -561,19 +561,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>h_01J0XJSQN5JF15J4QRHM139X82</t>
+          <t>h_01M2NCNZEJD0YKKKNYAWE87SRQ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Actions-on-Integrations/#h_01J0XJSQN5JF15J4QRHM139X82</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Actions-on-Integrations/#h_01M2NCNZEJD0YKKKNYAWE87SRQ</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>View Latest Logs</t>
+          <t>View Logs</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -583,19 +583,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01J0XHWEDT6V5B5B2J7NS5VQX7</t>
+          <t>h_01J0XJSQN5JF15J4QRHM139X82</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Actions-on-Integrations/#h_01J0XHWEDT6V5B5B2J7NS5VQX7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Actions-on-Integrations/#h_01J0XJSQN5JF15J4QRHM139X82</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Export and Import Integration</t>
+          <t>View Latest Logs</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -605,19 +605,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01JD1FAN5A7AR273MX0SF7BE1Q</t>
+          <t>h_01J0XHWEDT6V5B5B2J7NS5VQX7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Actions-on-Integrations/#h_01JD1FAN5A7AR273MX0SF7BE1Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Actions-on-Integrations/#h_01J0XHWEDT6V5B5B2J7NS5VQX7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>View Execution Status and Timeline</t>
+          <t>Export and Import Integration</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -627,19 +627,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01J14TF95K8AV1NWQ0WW5BFRJX</t>
+          <t>h_01JD1FAN5A7AR273MX0SF7BE1Q</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Actions-on-Integrations/#h_01J14TF95K8AV1NWQ0WW5BFRJX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Actions-on-Integrations/#h_01JD1FAN5A7AR273MX0SF7BE1Q</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Upgrade an Integration</t>
+          <t>View Execution Status and Timeline</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -649,19 +649,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
+          <t>h_01J14TF95K8AV1NWQ0WW5BFRJX</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Actions-on-Integrations/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Actions-on-Integrations/#h_01J14TF95K8AV1NWQ0WW5BFRJX</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Download Integration Report</t>
+          <t>Upgrade an Integration</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01J0XHZZ1B75PCM4EG9QRV2TEV</t>
+          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Actions-on-Integrations/#h_01J0XHZZ1B75PCM4EG9QRV2TEV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Actions-on-Integrations/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Delete Integration</t>
+          <t>Download Integration Report</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,32 +693,54 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>01J0XJS4YFSZE9RB11B2RPXV57</t>
+          <t>h_01J0XHZZ1B75PCM4EG9QRV2TEV</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Actions-on-Integrations/#01J0XJS4YFSZE9RB11B2RPXV57</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Actions-on-Integrations/#h_01J0XHZZ1B75PCM4EG9QRV2TEV</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Delete Integration</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>01J0XJS4YFSZE9RB11B2RPXV57</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Actions-on-Integrations/#01J0XJS4YFSZE9RB11B2RPXV57</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>References</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>h_01H02H9WB603XRNADRN1EK60SB</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Actions-on-Integrations/#h_01H02H9WB603XRNADRN1EK60SB</t>
         </is>
